--- a/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4738</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13488</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15287</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28916</t>
+          <t>29624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10808</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>20986</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15155</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26233</t>
+          <t>26851</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28616</t>
+          <t>28849</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43283</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,27%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>10433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2336</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>19472</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29360</t>
+          <t>29365</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59003</t>
+          <t>60579</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13654</t>
+          <t>14342</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>25820</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42261</t>
+          <t>41426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90292</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4175</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24830</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6401</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16997</t>
+          <t>18071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35094</t>
+          <t>35985</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>1972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>531</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6572</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5057</t>
+          <t>5643</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8928</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>970</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1205</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12436</t>
+          <t>12976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18193</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>12099</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14114</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13909</t>
+          <t>13443</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24238</t>
+          <t>24265</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3726</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6615</t>
+          <t>7440</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5297</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13892</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13920</t>
+          <t>14504</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,6%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,5%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7298</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7483</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4354</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>821</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4695</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2366</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7926</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4284</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7850</t>
+          <t>7846</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7270</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13093</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18322</t>
+          <t>18238</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2692</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3327</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6325</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3790</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11348</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15326</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>12474</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33407</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,74%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>74,85%</t>
         </is>
       </c>
     </row>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4962</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>979</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>10092</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3538</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>15,65%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>14018</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>11819</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10991</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>21865</t>
+          <t>21969</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29503</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>30801</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>48088</t>
+          <t>48102</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1643</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>8705</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2437</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11269</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>15786</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>10236</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>7328</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>19431</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>23,37%</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3444</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2601</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>8895</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>19975</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>35807</t>
+          <t>35906</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>32863</t>
+          <t>32714</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>51941</t>
+          <t>51735</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>12927</t>
+          <t>12810</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>48,97%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>38417</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>40575</t>
+          <t>40189</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>59647</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,42%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>20976</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18831</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>27,14%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14274</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>30657</t>
+          <t>30333</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>52840</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>55157</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>139688</t>
+          <t>133228</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>83368</t>
+          <t>83941</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>122321</t>
+          <t>122257</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>212552</t>
+          <t>213062</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,25%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>64606</t>
+          <t>61501</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>108560</t>
+          <t>109571</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>109333</t>
+          <t>107996</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>140198</t>
+          <t>138537</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>180617</t>
+          <t>178196</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>239089</t>
+          <t>237279</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,71%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>21105</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>41481</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>31987</t>
+          <t>33090</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>53927</t>
+          <t>56497</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>60030</t>
+          <t>59626</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>92100</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>22758</t>
+          <t>22836</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>45477</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>21454</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>40222</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>50157</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>77968</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5995</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14568</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>34,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>20,95%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8327</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4423</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>12983</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,83%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>10756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>21862</t>
+          <t>16865</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15937</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>29624</t>
+          <t>22402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>16454</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>11786</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20259</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>57,5%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>41,19%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>70,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15153</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>10808</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20986</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>52,32%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>72,46%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>12191</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>8581</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26851</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>28645</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28849</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,84%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4909</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1604</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8896</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,71%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10433</t>
+          <t>9178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1675</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>575</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>585</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2536</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>436</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>5889</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2583</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6447</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>28964</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>28964</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>28964</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19472</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15159</t>
+          <t>14877</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29365</t>
+          <t>25602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>17973</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>12391</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23325</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,26%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>61,34%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>41721</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>20239</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>60579</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>60,56%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,38%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25820</t>
+          <t>21482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61540</t>
+          <t>32949</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41426</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89211</t>
+          <t>41672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9935</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16558</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>26,12%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>43,54%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>13181</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4175</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24400</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>19,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>35,42%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>19089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>23287</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35985</t>
+          <t>32216</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>359</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1694</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6313</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>358</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2438</t>
+          <t>2350</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>6376</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1199</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4569</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>2724</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7408</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5643</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>8394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38028</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38028</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38028</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>68889</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>68889</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>68889</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>80524</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>80524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>111068</t>
+          <t>80524</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5367</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,72%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>23,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3560</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,56%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>2716</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>970</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6215</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6665</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -2197,107 +2197,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>6705</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10906</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>4728</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2175</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>7960</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5027</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2431</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8424</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>23,93%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>11,57%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>40,1%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>11731</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>7744</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>16780</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>26,47%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
         <is>
           <t>37,86%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>8090</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>4749</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>12976</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>18,07%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>49,38%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>12817</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>8245</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>18691</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>27,1%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9161</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>5653</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12654</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>39,3%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>54,28%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>8824</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5456</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>12099</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>41,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14129</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24265</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1907</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5214</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,18%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1207</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3680</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5,74%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3829</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>635</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1311</t>
+          <t>1211</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7440</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3042</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5982</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13,05%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5614</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>9029</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>26,7%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>42,95%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>5397</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5297</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13892</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23312</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23312</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23312</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>21024</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>44322</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>44322</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>47300</t>
+          <t>44322</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3582</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>8294</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>23,2%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>8,11%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>53,72%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>4717</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>9231</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>20,91%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9,25%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,92%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14504</t>
+          <t>14696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,29%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3707</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>558</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>8523</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>55,21%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>4772</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>1848</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>9012</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>21,15%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>4417</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8789</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8125</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4187</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>14455</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4478</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>9065</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>29,01%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>58,71%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>7035</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>3773</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>11332</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>31,19%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>50,23%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>11583</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2663</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8603</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>55,72%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1052</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3913</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2631</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>7111</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>16,43%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>8903</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3577</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>941</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>9047</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>32,11%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>5089</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2361</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>9011</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>22,56%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>15439</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>15439</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>15439</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>22938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>38572</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>38572</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38572</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>792</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>7441</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>7297</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>11163</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>81,35%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>61,6%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>6389</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>4199</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>7846</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>73,96%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>9638</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11144</t>
+          <t>7652</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>12950</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18238</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>11845</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>11845</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>11845</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>8638</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>11965</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>20604</t>
+          <t>20391</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>517</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -4145,12 +4145,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>445</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2405</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>963</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>6425</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>3438</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>10135</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>14,92%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>43,98%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>3373</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>6359</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>18,83%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>35,51%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>10353</t>
+          <t>9814</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,95%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>14752</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>10651</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>17980</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>64,01%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>46,22%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>78,02%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>11397</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>8086</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>14251</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>11318</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>7724</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>14069</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>63,64%</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>45,15%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>79,58%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>17018</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>12576</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>20692</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>64,88%</t>
-        </is>
-      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>28415</t>
+          <t>26070</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22641</t>
+          <t>21055</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>30877</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,62%</t>
         </is>
       </c>
     </row>
@@ -4469,107 +4469,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>3998</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>17,35%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>4783</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>4685</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>18,23%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>6141</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1686</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>2670</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>979</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>5594</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>2631</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -4695,57 +4695,57 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>23045</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>23045</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>23045</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>44139</t>
+          <t>40829</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>3808</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>7724</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1134</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10092</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13551</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,85%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>7951</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>3668</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>13664</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>30,65%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>9798</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>5415</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>16482</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>8373</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>13737</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>18170</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>23220</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>21719</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>15321</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>27709</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>48,72%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>34,37%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>62,16%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>16258</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>10991</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>21969</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>41,66%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>28,16%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>56,29%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>21794</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>47,72%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>38963</t>
+          <t>38088</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>30801</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>48102</t>
+          <t>46092</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>5070</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>4,49%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>22,24%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>4332</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>1643</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>8705</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>11,1%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>22,31%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>16200</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>6029</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2460</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>10766</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>13,52%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>24,15%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>5229</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>2189</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>10236</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>13,4%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>26,23%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>7048</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12605</t>
+          <t>9560</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>10508</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>5872</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>44576</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>44576</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>44576</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>39025</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>39025</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>39025</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>36763</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>86604</t>
+          <t>81338</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>86604</t>
+          <t>81338</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>86604</t>
+          <t>81338</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,107 +5494,107 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2239</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>3444</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>4,33%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>2601</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>6044</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>11819</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>5117</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>2452</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>9392</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>5,01%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>12796</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>18150</t>
+          <t>17170</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>28140</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>20643</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>36233</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>34,98%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>25,66%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>45,04%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>13898</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>9500</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>19909</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>28,4%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>40,68%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>19975</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>35906</t>
+          <t>19572</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>42064</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>32714</t>
+          <t>33373</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>51735</t>
+          <t>51856</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>31986</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>23646</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>40806</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>29,39%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>50,73%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>18121</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>12810</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>23437</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>37,03%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>26,17%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>47,89%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>23042</t>
+          <t>13488</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>40052</t>
+          <t>24589</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>49115</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>60279</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -5946,72 +5946,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13779</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>8241</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>21040</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>17,13%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>11806</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>7384</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>17555</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>15,09%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>35,87%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>8530</t>
+          <t>7853</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>18506</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>25497</t>
+          <t>26323</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>18831</t>
+          <t>19137</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>34853</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>80443</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>80443</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>80443</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>48943</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>48943</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>48943</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>79550</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>79550</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>79550</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>128493</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>128493</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>128493</t>
+          <t>130561</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>19463</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>13761</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>7,34%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>18535</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>11043</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>27525</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>30333</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>40020</t>
+          <t>38688</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>29653</t>
+          <t>29266</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>52840</t>
+          <t>50287</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>60904</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>49828</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>74161</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>27,95%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>80084</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>55157</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>133228</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>69497</t>
+          <t>49985</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>83941</t>
+          <t>60425</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>149581</t>
+          <t>110889</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>122257</t>
+          <t>96899</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>213062</t>
+          <t>128802</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>114274</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>101455</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>129627</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>43,07%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>38,24%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>48,86%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>92135</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>61501</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>109571</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>24,03%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>42,81%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>123418</t>
+          <t>89354</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>107996</t>
+          <t>76759</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>138537</t>
+          <t>100597</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>215553</t>
+          <t>203628</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>178196</t>
+          <t>183742</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>237279</t>
+          <t>220710</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>33970</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>56378</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>21,25%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>31489</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>21105</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>42671</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>12,3%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>31848</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>33090</t>
+          <t>24441</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>56497</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>75281</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>59626</t>
+          <t>61414</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>92100</t>
+          <t>89110</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>27227</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>18777</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>37628</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>10,26%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>7,08%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>14,18%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>33707</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>22836</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>45477</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>13,17%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>8,92%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>17,77%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>43129</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>62982</t>
+          <t>60742</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>76545</t>
+          <t>74122</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>265302</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>350</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>255950</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>286877</t>
+          <t>223926</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>542827</t>
+          <t>489227</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
